--- a/Ódor Artúr/érettségi/26maj/rimini_noi.xlsx
+++ b/Ódor Artúr/érettségi/26maj/rimini_noi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c21c437aeb2245f/Dokumentumok/fakt2025/Ódor Artúr/érettségi/26maj/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\europa04\Documents\fakt2025\Ódor Artúr\érettségi\26maj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{BC6B7443-E9DF-424D-B284-B40AF7E21D87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3CF62982-47D9-4B38-9079-12D83901FD01}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F5E7D4-5985-4568-A00A-7979E7FE880E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{BC9FF6E8-34CB-42BD-95D9-5789FD7935BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{BC9FF6E8-34CB-42BD-95D9-5789FD7935BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,18 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -708,7 +720,7 @@
     <col min="29" max="29" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="10" customFormat="1" ht="108" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="10" customFormat="1" ht="107.25" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -811,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="4">
-        <f>SUM(F2:V2)</f>
+        <f t="shared" ref="E2:E33" si="0">SUM(F2:V2)</f>
         <v>4.6400462962962956E-2</v>
       </c>
       <c r="F2" s="3">
@@ -866,31 +878,31 @@
         <v>3.4027777777777784E-3</v>
       </c>
       <c r="W2" s="3">
-        <f>SUM(F2,H2,J2,L2,N2,P2,R2,T2)</f>
+        <f t="shared" ref="W2:W33" si="1">SUM(F2,H2,J2,L2,N2,P2,R2,T2)</f>
         <v>2.3240740740740742E-2</v>
       </c>
       <c r="X2" s="3">
-        <f>MIN(F2,H2,J2,L2,N2,P2,R2,T2)</f>
+        <f t="shared" ref="X2:X33" si="2">MIN(F2,H2,J2,L2,N2,P2,R2,T2)</f>
         <v>2.3842592592592591E-3</v>
       </c>
       <c r="Y2" s="3">
-        <f>W2/8</f>
+        <f t="shared" ref="Y2:Y33" si="3">W2/8</f>
         <v>2.9050925925925928E-3</v>
       </c>
       <c r="Z2" s="3">
-        <f>SUM(G2,I2,K2,M2,O2,Q2,S2,U2)</f>
+        <f t="shared" ref="Z2:Z33" si="4">SUM(G2,I2,K2,M2,O2,Q2,S2,U2)</f>
         <v>1.9756944444444442E-2</v>
       </c>
       <c r="AA2" s="3">
-        <f>AVERAGE(G2,I2,K2,M2,O2,Q2,S2,U2)</f>
+        <f t="shared" ref="AA2:AA33" si="5">AVERAGE(G2,I2,K2,M2,O2,Q2,S2,U2)</f>
         <v>2.4696180555555552E-3</v>
       </c>
       <c r="AB2" s="1">
-        <f>W2/E2</f>
+        <f t="shared" ref="AB2:AB33" si="6">W2/E2</f>
         <v>0.50087303566974317</v>
       </c>
       <c r="AC2" s="1">
-        <f>Z2/E2</f>
+        <f t="shared" ref="AC2:AC33" si="7">Z2/E2</f>
         <v>0.42579196807183839</v>
       </c>
     </row>
@@ -908,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="4">
-        <f>SUM(F3:V3)</f>
+        <f t="shared" si="0"/>
         <v>4.6990740740740729E-2</v>
       </c>
       <c r="F3" s="3">
@@ -963,31 +975,31 @@
         <v>3.7037037037037034E-3</v>
       </c>
       <c r="W3" s="3">
-        <f>SUM(F3,H3,J3,L3,N3,P3,R3,T3)</f>
+        <f t="shared" si="1"/>
         <v>2.3206018518518518E-2</v>
       </c>
       <c r="X3" s="3">
-        <f>MIN(F3,H3,J3,L3,N3,P3,R3,T3)</f>
+        <f t="shared" si="2"/>
         <v>2.4652777777777776E-3</v>
       </c>
       <c r="Y3" s="3">
-        <f>W3/8</f>
+        <f t="shared" si="3"/>
         <v>2.9007523148148148E-3</v>
       </c>
       <c r="Z3" s="3">
-        <f>SUM(G3,I3,K3,M3,O3,Q3,S3,U3)</f>
+        <f t="shared" si="4"/>
         <v>2.0081018518518519E-2</v>
       </c>
       <c r="AA3" s="3">
-        <f>AVERAGE(G3,I3,K3,M3,O3,Q3,S3,U3)</f>
+        <f t="shared" si="5"/>
         <v>2.5101273148148149E-3</v>
       </c>
       <c r="AB3" s="1">
-        <f>W3/E3</f>
+        <f t="shared" si="6"/>
         <v>0.49384236453201985</v>
       </c>
       <c r="AC3" s="1">
-        <f>Z3/E3</f>
+        <f t="shared" si="7"/>
         <v>0.42733990147783263</v>
       </c>
     </row>
@@ -1005,7 +1017,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4">
-        <f>SUM(F4:V4)</f>
+        <f t="shared" si="0"/>
         <v>4.701388888888889E-2</v>
       </c>
       <c r="F4" s="3">
@@ -1060,31 +1072,31 @@
         <v>3.2407407407407406E-3</v>
       </c>
       <c r="W4" s="3">
-        <f>SUM(F4,H4,J4,L4,N4,P4,R4,T4)</f>
+        <f t="shared" si="1"/>
         <v>2.2581018518518518E-2</v>
       </c>
       <c r="X4" s="3">
-        <f>MIN(F4,H4,J4,L4,N4,P4,R4,T4)</f>
+        <f t="shared" si="2"/>
         <v>2.1874999999999998E-3</v>
       </c>
       <c r="Y4" s="3">
-        <f>W4/8</f>
+        <f t="shared" si="3"/>
         <v>2.8226273148148147E-3</v>
       </c>
       <c r="Z4" s="3">
-        <f>SUM(G4,I4,K4,M4,O4,Q4,S4,U4)</f>
+        <f t="shared" si="4"/>
         <v>2.119212962962963E-2</v>
       </c>
       <c r="AA4" s="3">
-        <f>AVERAGE(G4,I4,K4,M4,O4,Q4,S4,U4)</f>
+        <f t="shared" si="5"/>
         <v>2.6490162037037038E-3</v>
       </c>
       <c r="AB4" s="1">
-        <f>W4/E4</f>
+        <f t="shared" si="6"/>
         <v>0.48030526834071885</v>
       </c>
       <c r="AC4" s="1">
-        <f>Z4/E4</f>
+        <f t="shared" si="7"/>
         <v>0.45076317085179712</v>
       </c>
     </row>
@@ -1102,7 +1114,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="4">
-        <f>SUM(F5:V5)</f>
+        <f t="shared" si="0"/>
         <v>4.7349537037037037E-2</v>
       </c>
       <c r="F5" s="3">
@@ -1157,31 +1169,31 @@
         <v>3.4606481481481485E-3</v>
       </c>
       <c r="W5" s="3">
-        <f>SUM(F5,H5,J5,L5,N5,P5,R5,T5)</f>
+        <f t="shared" si="1"/>
         <v>2.3055555555555555E-2</v>
       </c>
       <c r="X5" s="3">
-        <f>MIN(F5,H5,J5,L5,N5,P5,R5,T5)</f>
+        <f t="shared" si="2"/>
         <v>2.3611111111111111E-3</v>
       </c>
       <c r="Y5" s="3">
-        <f>W5/8</f>
+        <f t="shared" si="3"/>
         <v>2.8819444444444444E-3</v>
       </c>
       <c r="Z5" s="3">
-        <f>SUM(G5,I5,K5,M5,O5,Q5,S5,U5)</f>
+        <f t="shared" si="4"/>
         <v>2.0833333333333336E-2</v>
       </c>
       <c r="AA5" s="3">
-        <f>AVERAGE(G5,I5,K5,M5,O5,Q5,S5,U5)</f>
+        <f t="shared" si="5"/>
         <v>2.604166666666667E-3</v>
       </c>
       <c r="AB5" s="1">
-        <f>W5/E5</f>
+        <f t="shared" si="6"/>
         <v>0.48692251283304816</v>
       </c>
       <c r="AC5" s="1">
-        <f>Z5/E5</f>
+        <f t="shared" si="7"/>
         <v>0.43999022243950137</v>
       </c>
     </row>
@@ -1199,7 +1211,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="4">
-        <f>SUM(F6:V6)</f>
+        <f t="shared" si="0"/>
         <v>4.746527777777778E-2</v>
       </c>
       <c r="F6" s="3">
@@ -1254,31 +1266,31 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="W6" s="3">
-        <f>SUM(F6,H6,J6,L6,N6,P6,R6,T6)</f>
+        <f t="shared" si="1"/>
         <v>2.420138888888889E-2</v>
       </c>
       <c r="X6" s="3">
-        <f>MIN(F6,H6,J6,L6,N6,P6,R6,T6)</f>
+        <f t="shared" si="2"/>
         <v>2.4537037037037036E-3</v>
       </c>
       <c r="Y6" s="3">
-        <f>W6/8</f>
+        <f t="shared" si="3"/>
         <v>3.0251736111111113E-3</v>
       </c>
       <c r="Z6" s="3">
-        <f>SUM(G6,I6,K6,M6,O6,Q6,S6,U6)</f>
+        <f t="shared" si="4"/>
         <v>1.9791666666666666E-2</v>
       </c>
       <c r="AA6" s="3">
-        <f>AVERAGE(G6,I6,K6,M6,O6,Q6,S6,U6)</f>
+        <f t="shared" si="5"/>
         <v>2.4739583333333332E-3</v>
       </c>
       <c r="AB6" s="1">
-        <f>W6/E6</f>
+        <f t="shared" si="6"/>
         <v>0.50987564008778352</v>
       </c>
       <c r="AC6" s="1">
-        <f>Z6/E6</f>
+        <f t="shared" si="7"/>
         <v>0.41697147037307969</v>
       </c>
     </row>
@@ -1296,7 +1308,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="4">
-        <f>SUM(F7:V7)</f>
+        <f t="shared" si="0"/>
         <v>4.7812499999999994E-2</v>
       </c>
       <c r="F7" s="3">
@@ -1351,31 +1363,31 @@
         <v>3.5416666666666665E-3</v>
       </c>
       <c r="W7" s="3">
-        <f>SUM(F7,H7,J7,L7,N7,P7,R7,T7)</f>
+        <f t="shared" si="1"/>
         <v>2.3796296296296298E-2</v>
       </c>
       <c r="X7" s="3">
-        <f>MIN(F7,H7,J7,L7,N7,P7,R7,T7)</f>
+        <f t="shared" si="2"/>
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="Y7" s="3">
-        <f>W7/8</f>
+        <f t="shared" si="3"/>
         <v>2.9745370370370373E-3</v>
       </c>
       <c r="Z7" s="3">
-        <f>SUM(G7,I7,K7,M7,O7,Q7,S7,U7)</f>
+        <f t="shared" si="4"/>
         <v>2.0474537037037034E-2</v>
       </c>
       <c r="AA7" s="3">
-        <f>AVERAGE(G7,I7,K7,M7,O7,Q7,S7,U7)</f>
+        <f t="shared" si="5"/>
         <v>2.5593171296296293E-3</v>
       </c>
       <c r="AB7" s="1">
-        <f>W7/E7</f>
+        <f t="shared" si="6"/>
         <v>0.49770031469377884</v>
       </c>
       <c r="AC7" s="1">
-        <f>Z7/E7</f>
+        <f t="shared" si="7"/>
         <v>0.4282256112321472</v>
       </c>
     </row>
@@ -1393,7 +1405,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="4">
-        <f>SUM(F8:V8)</f>
+        <f t="shared" si="0"/>
         <v>4.8194444444444436E-2</v>
       </c>
       <c r="F8" s="3">
@@ -1448,31 +1460,31 @@
         <v>3.3912037037037036E-3</v>
       </c>
       <c r="W8" s="3">
-        <f>SUM(F8,H8,J8,L8,N8,P8,R8,T8)</f>
+        <f t="shared" si="1"/>
         <v>2.4537037037037034E-2</v>
       </c>
       <c r="X8" s="3">
-        <f>MIN(F8,H8,J8,L8,N8,P8,R8,T8)</f>
+        <f t="shared" si="2"/>
         <v>2.4189814814814816E-3</v>
       </c>
       <c r="Y8" s="3">
-        <f>W8/8</f>
+        <f t="shared" si="3"/>
         <v>3.0671296296296293E-3</v>
       </c>
       <c r="Z8" s="3">
-        <f>SUM(G8,I8,K8,M8,O8,Q8,S8,U8)</f>
+        <f t="shared" si="4"/>
         <v>2.0266203703703703E-2</v>
       </c>
       <c r="AA8" s="3">
-        <f>AVERAGE(G8,I8,K8,M8,O8,Q8,S8,U8)</f>
+        <f t="shared" si="5"/>
         <v>2.5332754629629629E-3</v>
       </c>
       <c r="AB8" s="1">
-        <f>W8/E8</f>
+        <f t="shared" si="6"/>
         <v>0.5091258405379443</v>
       </c>
       <c r="AC8" s="1">
-        <f>Z8/E8</f>
+        <f t="shared" si="7"/>
         <v>0.42050912584053801</v>
       </c>
     </row>
@@ -1490,7 +1502,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="4">
-        <f>SUM(F9:V9)</f>
+        <f t="shared" si="0"/>
         <v>4.8356481481481486E-2</v>
       </c>
       <c r="F9" s="3">
@@ -1545,31 +1557,31 @@
         <v>3.9236111111111112E-3</v>
       </c>
       <c r="W9" s="3">
-        <f>SUM(F9,H9,J9,L9,N9,P9,R9,T9)</f>
+        <f t="shared" si="1"/>
         <v>2.4988425925925928E-2</v>
       </c>
       <c r="X9" s="3">
-        <f>MIN(F9,H9,J9,L9,N9,P9,R9,T9)</f>
+        <f t="shared" si="2"/>
         <v>2.4421296296296296E-3</v>
       </c>
       <c r="Y9" s="3">
-        <f>W9/8</f>
+        <f t="shared" si="3"/>
         <v>3.123553240740741E-3</v>
       </c>
       <c r="Z9" s="3">
-        <f>SUM(G9,I9,K9,M9,O9,Q9,S9,U9)</f>
+        <f t="shared" si="4"/>
         <v>1.9444444444444445E-2</v>
       </c>
       <c r="AA9" s="3">
-        <f>AVERAGE(G9,I9,K9,M9,O9,Q9,S9,U9)</f>
+        <f t="shared" si="5"/>
         <v>2.4305555555555556E-3</v>
       </c>
       <c r="AB9" s="1">
-        <f>W9/E9</f>
+        <f t="shared" si="6"/>
         <v>0.51675442795595983</v>
       </c>
       <c r="AC9" s="1">
-        <f>Z9/E9</f>
+        <f t="shared" si="7"/>
         <v>0.40210627094303492</v>
       </c>
     </row>
@@ -1587,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="4">
-        <f>SUM(F10:V10)</f>
+        <f t="shared" si="0"/>
         <v>4.8414351851851861E-2</v>
       </c>
       <c r="F10" s="3">
@@ -1642,31 +1654,31 @@
         <v>3.5763888888888894E-3</v>
       </c>
       <c r="W10" s="3">
-        <f>SUM(F10,H10,J10,L10,N10,P10,R10,T10)</f>
+        <f t="shared" si="1"/>
         <v>2.402777777777778E-2</v>
       </c>
       <c r="X10" s="3">
-        <f>MIN(F10,H10,J10,L10,N10,P10,R10,T10)</f>
+        <f t="shared" si="2"/>
         <v>2.3726851851851851E-3</v>
       </c>
       <c r="Y10" s="3">
-        <f>W10/8</f>
+        <f t="shared" si="3"/>
         <v>3.0034722222222225E-3</v>
       </c>
       <c r="Z10" s="3">
-        <f>SUM(G10,I10,K10,M10,O10,Q10,S10,U10)</f>
+        <f t="shared" si="4"/>
         <v>2.0810185185185182E-2</v>
       </c>
       <c r="AA10" s="3">
-        <f>AVERAGE(G10,I10,K10,M10,O10,Q10,S10,U10)</f>
+        <f t="shared" si="5"/>
         <v>2.6012731481481477E-3</v>
       </c>
       <c r="AB10" s="1">
-        <f>W10/E10</f>
+        <f t="shared" si="6"/>
         <v>0.49629452546019598</v>
       </c>
       <c r="AC10" s="1">
-        <f>Z10/E10</f>
+        <f t="shared" si="7"/>
         <v>0.42983504661726019</v>
       </c>
     </row>
@@ -1684,7 +1696,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
-        <f>SUM(F11:V11)</f>
+        <f t="shared" si="0"/>
         <v>4.8483796296296289E-2</v>
       </c>
       <c r="F11" s="3">
@@ -1739,31 +1751,31 @@
         <v>3.9120370370370368E-3</v>
       </c>
       <c r="W11" s="3">
-        <f>SUM(F11,H11,J11,L11,N11,P11,R11,T11)</f>
+        <f t="shared" si="1"/>
         <v>2.4120370370370375E-2</v>
       </c>
       <c r="X11" s="3">
-        <f>MIN(F11,H11,J11,L11,N11,P11,R11,T11)</f>
+        <f t="shared" si="2"/>
         <v>2.3611111111111111E-3</v>
       </c>
       <c r="Y11" s="3">
-        <f>W11/8</f>
+        <f t="shared" si="3"/>
         <v>3.0150462962962969E-3</v>
       </c>
       <c r="Z11" s="3">
-        <f>SUM(G11,I11,K11,M11,O11,Q11,S11,U11)</f>
+        <f t="shared" si="4"/>
         <v>2.0451388888888887E-2</v>
       </c>
       <c r="AA11" s="3">
-        <f>AVERAGE(G11,I11,K11,M11,O11,Q11,S11,U11)</f>
+        <f t="shared" si="5"/>
         <v>2.5564236111111109E-3</v>
       </c>
       <c r="AB11" s="1">
-        <f>W11/E11</f>
+        <f t="shared" si="6"/>
         <v>0.49749343518739575</v>
       </c>
       <c r="AC11" s="1">
-        <f>Z11/E11</f>
+        <f t="shared" si="7"/>
         <v>0.42181904989257585</v>
       </c>
     </row>
@@ -1781,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="4">
-        <f>SUM(F12:V12)</f>
+        <f t="shared" si="0"/>
         <v>4.8483796296296296E-2</v>
       </c>
       <c r="F12" s="3">
@@ -1836,31 +1848,31 @@
         <v>3.9467592592592592E-3</v>
       </c>
       <c r="W12" s="3">
-        <f>SUM(F12,H12,J12,L12,N12,P12,R12,T12)</f>
+        <f t="shared" si="1"/>
         <v>2.3402777777777776E-2</v>
       </c>
       <c r="X12" s="3">
-        <f>MIN(F12,H12,J12,L12,N12,P12,R12,T12)</f>
+        <f t="shared" si="2"/>
         <v>2.4074074074074076E-3</v>
       </c>
       <c r="Y12" s="3">
-        <f>W12/8</f>
+        <f t="shared" si="3"/>
         <v>2.925347222222222E-3</v>
       </c>
       <c r="Z12" s="3">
-        <f>SUM(G12,I12,K12,M12,O12,Q12,S12,U12)</f>
+        <f t="shared" si="4"/>
         <v>2.1134259259259262E-2</v>
       </c>
       <c r="AA12" s="3">
-        <f>AVERAGE(G12,I12,K12,M12,O12,Q12,S12,U12)</f>
+        <f t="shared" si="5"/>
         <v>2.6417824074074078E-3</v>
       </c>
       <c r="AB12" s="1">
-        <f>W12/E12</f>
+        <f t="shared" si="6"/>
         <v>0.48269276677011219</v>
       </c>
       <c r="AC12" s="1">
-        <f>Z12/E12</f>
+        <f t="shared" si="7"/>
         <v>0.43590355693482941</v>
       </c>
     </row>
@@ -1878,7 +1890,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="4">
-        <f>SUM(F13:V13)</f>
+        <f t="shared" si="0"/>
         <v>4.8796296296296296E-2</v>
       </c>
       <c r="F13" s="3">
@@ -1933,31 +1945,31 @@
         <v>4.2708333333333339E-3</v>
       </c>
       <c r="W13" s="3">
-        <f>SUM(F13,H13,J13,L13,N13,P13,R13,T13)</f>
+        <f t="shared" si="1"/>
         <v>2.1423611111111112E-2</v>
       </c>
       <c r="X13" s="3">
-        <f>MIN(F13,H13,J13,L13,N13,P13,R13,T13)</f>
+        <f t="shared" si="2"/>
         <v>2.1296296296296298E-3</v>
       </c>
       <c r="Y13" s="3">
-        <f>W13/8</f>
+        <f t="shared" si="3"/>
         <v>2.677951388888889E-3</v>
       </c>
       <c r="Z13" s="3">
-        <f>SUM(G13,I13,K13,M13,O13,Q13,S13,U13)</f>
+        <f t="shared" si="4"/>
         <v>2.3101851851851853E-2</v>
       </c>
       <c r="AA13" s="3">
-        <f>AVERAGE(G13,I13,K13,M13,O13,Q13,S13,U13)</f>
+        <f t="shared" si="5"/>
         <v>2.8877314814814816E-3</v>
       </c>
       <c r="AB13" s="1">
-        <f>W13/E13</f>
+        <f t="shared" si="6"/>
         <v>0.43904174573055033</v>
       </c>
       <c r="AC13" s="1">
-        <f>Z13/E13</f>
+        <f t="shared" si="7"/>
         <v>0.47343453510436434</v>
       </c>
     </row>
@@ -1975,7 +1987,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="4">
-        <f>SUM(F14:V14)</f>
+        <f t="shared" si="0"/>
         <v>4.884259259259259E-2</v>
       </c>
       <c r="F14" s="3">
@@ -2030,31 +2042,31 @@
         <v>3.6111111111111114E-3</v>
       </c>
       <c r="W14" s="3">
-        <f>SUM(F14,H14,J14,L14,N14,P14,R14,T14)</f>
+        <f t="shared" si="1"/>
         <v>2.3784722222222224E-2</v>
       </c>
       <c r="X14" s="3">
-        <f>MIN(F14,H14,J14,L14,N14,P14,R14,T14)</f>
+        <f t="shared" si="2"/>
         <v>2.4421296296296296E-3</v>
       </c>
       <c r="Y14" s="3">
-        <f>W14/8</f>
+        <f t="shared" si="3"/>
         <v>2.9730902777777781E-3</v>
       </c>
       <c r="Z14" s="3">
-        <f>SUM(G14,I14,K14,M14,O14,Q14,S14,U14)</f>
+        <f t="shared" si="4"/>
         <v>2.1446759259259259E-2</v>
       </c>
       <c r="AA14" s="3">
-        <f>AVERAGE(G14,I14,K14,M14,O14,Q14,S14,U14)</f>
+        <f t="shared" si="5"/>
         <v>2.6808449074074074E-3</v>
       </c>
       <c r="AB14" s="1">
-        <f>W14/E14</f>
+        <f t="shared" si="6"/>
         <v>0.48696682464454982</v>
       </c>
       <c r="AC14" s="1">
-        <f>Z14/E14</f>
+        <f t="shared" si="7"/>
         <v>0.43909952606635072</v>
       </c>
     </row>
@@ -2072,7 +2084,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="4">
-        <f>SUM(F15:V15)</f>
+        <f t="shared" si="0"/>
         <v>4.8912037037037046E-2</v>
       </c>
       <c r="F15" s="3">
@@ -2127,31 +2139,31 @@
         <v>3.8888888888888883E-3</v>
       </c>
       <c r="W15" s="3">
-        <f>SUM(F15,H15,J15,L15,N15,P15,R15,T15)</f>
+        <f t="shared" si="1"/>
         <v>2.4826388888888884E-2</v>
       </c>
       <c r="X15" s="3">
-        <f>MIN(F15,H15,J15,L15,N15,P15,R15,T15)</f>
+        <f t="shared" si="2"/>
         <v>2.5115740740740741E-3</v>
       </c>
       <c r="Y15" s="3">
-        <f>W15/8</f>
+        <f t="shared" si="3"/>
         <v>3.1032986111111105E-3</v>
       </c>
       <c r="Z15" s="3">
-        <f>SUM(G15,I15,K15,M15,O15,Q15,S15,U15)</f>
+        <f t="shared" si="4"/>
         <v>2.0196759259259262E-2</v>
       </c>
       <c r="AA15" s="3">
-        <f>AVERAGE(G15,I15,K15,M15,O15,Q15,S15,U15)</f>
+        <f t="shared" si="5"/>
         <v>2.5245949074074077E-3</v>
       </c>
       <c r="AB15" s="1">
-        <f>W15/E15</f>
+        <f t="shared" si="6"/>
         <v>0.50757217226691886</v>
       </c>
       <c r="AC15" s="1">
-        <f>Z15/E15</f>
+        <f t="shared" si="7"/>
         <v>0.41292001893043062</v>
       </c>
     </row>
@@ -2169,7 +2181,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="4">
-        <f>SUM(F16:V16)</f>
+        <f t="shared" si="0"/>
         <v>4.9004629629629627E-2</v>
       </c>
       <c r="F16" s="3">
@@ -2224,31 +2236,31 @@
         <v>3.6805555555555554E-3</v>
       </c>
       <c r="W16" s="3">
-        <f>SUM(F16,H16,J16,L16,N16,P16,R16,T16)</f>
+        <f t="shared" si="1"/>
         <v>2.1898148148148146E-2</v>
       </c>
       <c r="X16" s="3">
-        <f>MIN(F16,H16,J16,L16,N16,P16,R16,T16)</f>
+        <f t="shared" si="2"/>
         <v>2.2222222222222222E-3</v>
       </c>
       <c r="Y16" s="3">
-        <f>W16/8</f>
+        <f t="shared" si="3"/>
         <v>2.7372685185185182E-3</v>
       </c>
       <c r="Z16" s="3">
-        <f>SUM(G16,I16,K16,M16,O16,Q16,S16,U16)</f>
+        <f t="shared" si="4"/>
         <v>2.3425925925925926E-2</v>
       </c>
       <c r="AA16" s="3">
-        <f>AVERAGE(G16,I16,K16,M16,O16,Q16,S16,U16)</f>
+        <f t="shared" si="5"/>
         <v>2.9282407407407408E-3</v>
       </c>
       <c r="AB16" s="1">
-        <f>W16/E16</f>
+        <f t="shared" si="6"/>
         <v>0.44685876239962208</v>
       </c>
       <c r="AC16" s="1">
-        <f>Z16/E16</f>
+        <f t="shared" si="7"/>
         <v>0.47803495512517719</v>
       </c>
     </row>
@@ -2266,7 +2278,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="4">
-        <f>SUM(F17:V17)</f>
+        <f t="shared" si="0"/>
         <v>4.9062499999999995E-2</v>
       </c>
       <c r="F17" s="3">
@@ -2321,31 +2333,31 @@
         <v>3.9120370370370368E-3</v>
       </c>
       <c r="W17" s="3">
-        <f>SUM(F17,H17,J17,L17,N17,P17,R17,T17)</f>
+        <f t="shared" si="1"/>
         <v>2.3321759259259257E-2</v>
       </c>
       <c r="X17" s="3">
-        <f>MIN(F17,H17,J17,L17,N17,P17,R17,T17)</f>
+        <f t="shared" si="2"/>
         <v>2.2685185185185182E-3</v>
       </c>
       <c r="Y17" s="3">
-        <f>W17/8</f>
+        <f t="shared" si="3"/>
         <v>2.9152199074074072E-3</v>
       </c>
       <c r="Z17" s="3">
-        <f>SUM(G17,I17,K17,M17,O17,Q17,S17,U17)</f>
+        <f t="shared" si="4"/>
         <v>2.1828703703703704E-2</v>
       </c>
       <c r="AA17" s="3">
-        <f>AVERAGE(G17,I17,K17,M17,O17,Q17,S17,U17)</f>
+        <f t="shared" si="5"/>
         <v>2.728587962962963E-3</v>
       </c>
       <c r="AB17" s="1">
-        <f>W17/E17</f>
+        <f t="shared" si="6"/>
         <v>0.47534795942439256</v>
       </c>
       <c r="AC17" s="1">
-        <f>Z17/E17</f>
+        <f t="shared" si="7"/>
         <v>0.44491625383345135</v>
       </c>
     </row>
@@ -2363,7 +2375,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="4">
-        <f>SUM(F18:V18)</f>
+        <f t="shared" si="0"/>
         <v>4.9074074074074076E-2</v>
       </c>
       <c r="F18" s="3">
@@ -2418,31 +2430,31 @@
         <v>3.4490740740740745E-3</v>
       </c>
       <c r="W18" s="3">
-        <f>SUM(F18,H18,J18,L18,N18,P18,R18,T18)</f>
+        <f t="shared" si="1"/>
         <v>2.2453703703703701E-2</v>
       </c>
       <c r="X18" s="3">
-        <f>MIN(F18,H18,J18,L18,N18,P18,R18,T18)</f>
+        <f t="shared" si="2"/>
         <v>2.2685185185185182E-3</v>
       </c>
       <c r="Y18" s="3">
-        <f>W18/8</f>
+        <f t="shared" si="3"/>
         <v>2.8067129629629627E-3</v>
       </c>
       <c r="Z18" s="3">
-        <f>SUM(G18,I18,K18,M18,O18,Q18,S18,U18)</f>
+        <f t="shared" si="4"/>
         <v>2.3171296296296297E-2</v>
       </c>
       <c r="AA18" s="3">
-        <f>AVERAGE(G18,I18,K18,M18,O18,Q18,S18,U18)</f>
+        <f t="shared" si="5"/>
         <v>2.8964120370370372E-3</v>
       </c>
       <c r="AB18" s="1">
-        <f>W18/E18</f>
+        <f t="shared" si="6"/>
         <v>0.45754716981132071</v>
       </c>
       <c r="AC18" s="1">
-        <f>Z18/E18</f>
+        <f t="shared" si="7"/>
         <v>0.47216981132075475</v>
       </c>
     </row>
@@ -2460,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="4">
-        <f>SUM(F19:V19)</f>
+        <f t="shared" si="0"/>
         <v>4.9212962962962972E-2</v>
       </c>
       <c r="F19" s="3">
@@ -2515,31 +2527,31 @@
         <v>3.8194444444444443E-3</v>
       </c>
       <c r="W19" s="3">
-        <f>SUM(F19,H19,J19,L19,N19,P19,R19,T19)</f>
+        <f t="shared" si="1"/>
         <v>2.5162037037037035E-2</v>
       </c>
       <c r="X19" s="3">
-        <f>MIN(F19,H19,J19,L19,N19,P19,R19,T19)</f>
+        <f t="shared" si="2"/>
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="Y19" s="3">
-        <f>W19/8</f>
+        <f t="shared" si="3"/>
         <v>3.1452546296296294E-3</v>
       </c>
       <c r="Z19" s="3">
-        <f>SUM(G19,I19,K19,M19,O19,Q19,S19,U19)</f>
+        <f t="shared" si="4"/>
         <v>2.0231481481481482E-2</v>
       </c>
       <c r="AA19" s="3">
-        <f>AVERAGE(G19,I19,K19,M19,O19,Q19,S19,U19)</f>
+        <f t="shared" si="5"/>
         <v>2.5289351851851853E-3</v>
       </c>
       <c r="AB19" s="1">
-        <f>W19/E19</f>
+        <f t="shared" si="6"/>
         <v>0.51128880526810894</v>
       </c>
       <c r="AC19" s="1">
-        <f>Z19/E19</f>
+        <f t="shared" si="7"/>
         <v>0.41110065851364058</v>
       </c>
     </row>
@@ -2557,7 +2569,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="4">
-        <f>SUM(F20:V20)</f>
+        <f t="shared" si="0"/>
         <v>4.9317129629629634E-2</v>
       </c>
       <c r="F20" s="3">
@@ -2612,31 +2624,31 @@
         <v>3.8310185185185183E-3</v>
       </c>
       <c r="W20" s="3">
-        <f>SUM(F20,H20,J20,L20,N20,P20,R20,T20)</f>
+        <f t="shared" si="1"/>
         <v>2.5960648148148149E-2</v>
       </c>
       <c r="X20" s="3">
-        <f>MIN(F20,H20,J20,L20,N20,P20,R20,T20)</f>
+        <f t="shared" si="2"/>
         <v>2.627314814814815E-3</v>
       </c>
       <c r="Y20" s="3">
-        <f>W20/8</f>
+        <f t="shared" si="3"/>
         <v>3.2450810185185187E-3</v>
       </c>
       <c r="Z20" s="3">
-        <f>SUM(G20,I20,K20,M20,O20,Q20,S20,U20)</f>
+        <f t="shared" si="4"/>
         <v>1.9525462962962963E-2</v>
       </c>
       <c r="AA20" s="3">
-        <f>AVERAGE(G20,I20,K20,M20,O20,Q20,S20,U20)</f>
+        <f t="shared" si="5"/>
         <v>2.4406828703703704E-3</v>
       </c>
       <c r="AB20" s="1">
-        <f>W20/E20</f>
+        <f t="shared" si="6"/>
         <v>0.52640225299225529</v>
       </c>
       <c r="AC20" s="1">
-        <f>Z20/E20</f>
+        <f t="shared" si="7"/>
         <v>0.39591645153719779</v>
       </c>
     </row>
@@ -2654,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="4">
-        <f>SUM(F21:V21)</f>
+        <f t="shared" si="0"/>
         <v>4.9675925925925929E-2</v>
       </c>
       <c r="F21" s="3">
@@ -2709,31 +2721,31 @@
         <v>4.108796296296297E-3</v>
       </c>
       <c r="W21" s="3">
-        <f>SUM(F21,H21,J21,L21,N21,P21,R21,T21)</f>
+        <f t="shared" si="1"/>
         <v>2.3657407407407408E-2</v>
       </c>
       <c r="X21" s="3">
-        <f>MIN(F21,H21,J21,L21,N21,P21,R21,T21)</f>
+        <f t="shared" si="2"/>
         <v>2.4652777777777776E-3</v>
       </c>
       <c r="Y21" s="3">
-        <f>W21/8</f>
+        <f t="shared" si="3"/>
         <v>2.957175925925926E-3</v>
       </c>
       <c r="Z21" s="3">
-        <f>SUM(G21,I21,K21,M21,O21,Q21,S21,U21)</f>
+        <f t="shared" si="4"/>
         <v>2.1909722222222219E-2</v>
       </c>
       <c r="AA21" s="3">
-        <f>AVERAGE(G21,I21,K21,M21,O21,Q21,S21,U21)</f>
+        <f t="shared" si="5"/>
         <v>2.7387152777777774E-3</v>
       </c>
       <c r="AB21" s="1">
-        <f>W21/E21</f>
+        <f t="shared" si="6"/>
         <v>0.47623485554520034</v>
       </c>
       <c r="AC21" s="1">
-        <f>Z21/E21</f>
+        <f t="shared" si="7"/>
         <v>0.44105312208760478</v>
       </c>
     </row>
@@ -2751,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="4">
-        <f>SUM(F22:V22)</f>
+        <f t="shared" si="0"/>
         <v>4.9687499999999996E-2</v>
       </c>
       <c r="F22" s="3">
@@ -2806,31 +2818,31 @@
         <v>4.2129629629629626E-3</v>
       </c>
       <c r="W22" s="3">
-        <f>SUM(F22,H22,J22,L22,N22,P22,R22,T22)</f>
+        <f t="shared" si="1"/>
         <v>2.4537037037037038E-2</v>
       </c>
       <c r="X22" s="3">
-        <f>MIN(F22,H22,J22,L22,N22,P22,R22,T22)</f>
+        <f t="shared" si="2"/>
         <v>2.4537037037037036E-3</v>
       </c>
       <c r="Y22" s="3">
-        <f>W22/8</f>
+        <f t="shared" si="3"/>
         <v>3.0671296296296297E-3</v>
       </c>
       <c r="Z22" s="3">
-        <f>SUM(G22,I22,K22,M22,O22,Q22,S22,U22)</f>
+        <f t="shared" si="4"/>
         <v>2.0937500000000001E-2</v>
       </c>
       <c r="AA22" s="3">
-        <f>AVERAGE(G22,I22,K22,M22,O22,Q22,S22,U22)</f>
+        <f t="shared" si="5"/>
         <v>2.6171875000000002E-3</v>
       </c>
       <c r="AB22" s="1">
-        <f>W22/E22</f>
+        <f t="shared" si="6"/>
         <v>0.49382716049382724</v>
       </c>
       <c r="AC22" s="1">
-        <f>Z22/E22</f>
+        <f t="shared" si="7"/>
         <v>0.42138364779874221</v>
       </c>
     </row>
@@ -2848,7 +2860,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="4">
-        <f>SUM(F23:V23)</f>
+        <f t="shared" si="0"/>
         <v>4.9768518518518517E-2</v>
       </c>
       <c r="F23" s="3">
@@ -2903,31 +2915,31 @@
         <v>4.1203703703703706E-3</v>
       </c>
       <c r="W23" s="3">
-        <f>SUM(F23,H23,J23,L23,N23,P23,R23,T23)</f>
+        <f t="shared" si="1"/>
         <v>2.4537037037037038E-2</v>
       </c>
       <c r="X23" s="3">
-        <f>MIN(F23,H23,J23,L23,N23,P23,R23,T23)</f>
+        <f t="shared" si="2"/>
         <v>2.5231481481481481E-3</v>
       </c>
       <c r="Y23" s="3">
-        <f>W23/8</f>
+        <f t="shared" si="3"/>
         <v>3.0671296296296297E-3</v>
       </c>
       <c r="Z23" s="3">
-        <f>SUM(G23,I23,K23,M23,O23,Q23,S23,U23)</f>
+        <f t="shared" si="4"/>
         <v>2.1111111111111112E-2</v>
       </c>
       <c r="AA23" s="3">
-        <f>AVERAGE(G23,I23,K23,M23,O23,Q23,S23,U23)</f>
+        <f t="shared" si="5"/>
         <v>2.638888888888889E-3</v>
       </c>
       <c r="AB23" s="1">
-        <f>W23/E23</f>
+        <f t="shared" si="6"/>
         <v>0.49302325581395351</v>
       </c>
       <c r="AC23" s="1">
-        <f>Z23/E23</f>
+        <f t="shared" si="7"/>
         <v>0.42418604651162795</v>
       </c>
     </row>
@@ -2945,7 +2957,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="4">
-        <f>SUM(F24:V24)</f>
+        <f t="shared" si="0"/>
         <v>4.9791666666666665E-2</v>
       </c>
       <c r="F24" s="3">
@@ -3000,31 +3012,31 @@
         <v>3.6342592592592594E-3</v>
       </c>
       <c r="W24" s="3">
-        <f>SUM(F24,H24,J24,L24,N24,P24,R24,T24)</f>
+        <f t="shared" si="1"/>
         <v>2.4421296296296295E-2</v>
       </c>
       <c r="X24" s="3">
-        <f>MIN(F24,H24,J24,L24,N24,P24,R24,T24)</f>
+        <f t="shared" si="2"/>
         <v>2.4652777777777776E-3</v>
       </c>
       <c r="Y24" s="3">
-        <f>W24/8</f>
+        <f t="shared" si="3"/>
         <v>3.0526620370370369E-3</v>
       </c>
       <c r="Z24" s="3">
-        <f>SUM(G24,I24,K24,M24,O24,Q24,S24,U24)</f>
+        <f t="shared" si="4"/>
         <v>2.1736111111111109E-2</v>
       </c>
       <c r="AA24" s="3">
-        <f>AVERAGE(G24,I24,K24,M24,O24,Q24,S24,U24)</f>
+        <f t="shared" si="5"/>
         <v>2.7170138888888886E-3</v>
       </c>
       <c r="AB24" s="1">
-        <f>W24/E24</f>
+        <f t="shared" si="6"/>
         <v>0.49046954904695489</v>
       </c>
       <c r="AC24" s="1">
-        <f>Z24/E24</f>
+        <f t="shared" si="7"/>
         <v>0.43654114365411434</v>
       </c>
     </row>
@@ -3042,7 +3054,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="4">
-        <f>SUM(F25:V25)</f>
+        <f t="shared" si="0"/>
         <v>4.9918981481481481E-2</v>
       </c>
       <c r="F25" s="3">
@@ -3097,31 +3109,31 @@
         <v>3.8657407407407408E-3</v>
       </c>
       <c r="W25" s="3">
-        <f>SUM(F25,H25,J25,L25,N25,P25,R25,T25)</f>
+        <f t="shared" si="1"/>
         <v>2.5104166666666667E-2</v>
       </c>
       <c r="X25" s="3">
-        <f>MIN(F25,H25,J25,L25,N25,P25,R25,T25)</f>
+        <f t="shared" si="2"/>
         <v>2.488425925925926E-3</v>
       </c>
       <c r="Y25" s="3">
-        <f>W25/8</f>
+        <f t="shared" si="3"/>
         <v>3.1380208333333334E-3</v>
       </c>
       <c r="Z25" s="3">
-        <f>SUM(G25,I25,K25,M25,O25,Q25,S25,U25)</f>
+        <f t="shared" si="4"/>
         <v>2.0949074074074075E-2</v>
       </c>
       <c r="AA25" s="3">
-        <f>AVERAGE(G25,I25,K25,M25,O25,Q25,S25,U25)</f>
+        <f t="shared" si="5"/>
         <v>2.6186342592592594E-3</v>
       </c>
       <c r="AB25" s="1">
-        <f>W25/E25</f>
+        <f t="shared" si="6"/>
         <v>0.50289821469974494</v>
       </c>
       <c r="AC25" s="1">
-        <f>Z25/E25</f>
+        <f t="shared" si="7"/>
         <v>0.41966148852306984</v>
       </c>
     </row>
@@ -3139,7 +3151,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="4">
-        <f>SUM(F26:V26)</f>
+        <f t="shared" si="0"/>
         <v>5.004629629629629E-2</v>
       </c>
       <c r="F26" s="3">
@@ -3194,31 +3206,31 @@
         <v>3.9583333333333337E-3</v>
       </c>
       <c r="W26" s="3">
-        <f>SUM(F26,H26,J26,L26,N26,P26,R26,T26)</f>
+        <f t="shared" si="1"/>
         <v>2.4768518518518516E-2</v>
       </c>
       <c r="X26" s="3">
-        <f>MIN(F26,H26,J26,L26,N26,P26,R26,T26)</f>
+        <f t="shared" si="2"/>
         <v>2.5925925925925925E-3</v>
       </c>
       <c r="Y26" s="3">
-        <f>W26/8</f>
+        <f t="shared" si="3"/>
         <v>3.0960648148148145E-3</v>
       </c>
       <c r="Z26" s="3">
-        <f>SUM(G26,I26,K26,M26,O26,Q26,S26,U26)</f>
+        <f t="shared" si="4"/>
         <v>2.1319444444444446E-2</v>
       </c>
       <c r="AA26" s="3">
-        <f>AVERAGE(G26,I26,K26,M26,O26,Q26,S26,U26)</f>
+        <f t="shared" si="5"/>
         <v>2.6649305555555558E-3</v>
       </c>
       <c r="AB26" s="1">
-        <f>W26/E26</f>
+        <f t="shared" si="6"/>
         <v>0.49491211840888066</v>
       </c>
       <c r="AC26" s="1">
-        <f>Z26/E26</f>
+        <f t="shared" si="7"/>
         <v>0.42599444958371885</v>
       </c>
     </row>
@@ -3236,7 +3248,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="4">
-        <f>SUM(F27:V27)</f>
+        <f t="shared" si="0"/>
         <v>5.0092592592592598E-2</v>
       </c>
       <c r="F27" s="3">
@@ -3291,31 +3303,31 @@
         <v>4.108796296296297E-3</v>
       </c>
       <c r="W27" s="3">
-        <f>SUM(F27,H27,J27,L27,N27,P27,R27,T27)</f>
+        <f t="shared" si="1"/>
         <v>2.5636574074074076E-2</v>
       </c>
       <c r="X27" s="3">
-        <f>MIN(F27,H27,J27,L27,N27,P27,R27,T27)</f>
+        <f t="shared" si="2"/>
         <v>2.673611111111111E-3</v>
       </c>
       <c r="Y27" s="3">
-        <f>W27/8</f>
+        <f t="shared" si="3"/>
         <v>3.2045717592592594E-3</v>
       </c>
       <c r="Z27" s="3">
-        <f>SUM(G27,I27,K27,M27,O27,Q27,S27,U27)</f>
+        <f t="shared" si="4"/>
         <v>2.0347222222222221E-2</v>
       </c>
       <c r="AA27" s="3">
-        <f>AVERAGE(G27,I27,K27,M27,O27,Q27,S27,U27)</f>
+        <f t="shared" si="5"/>
         <v>2.5434027777777777E-3</v>
       </c>
       <c r="AB27" s="1">
-        <f>W27/E27</f>
+        <f t="shared" si="6"/>
         <v>0.51178373382624764</v>
       </c>
       <c r="AC27" s="1">
-        <f>Z27/E27</f>
+        <f t="shared" si="7"/>
         <v>0.40619223659889087</v>
       </c>
     </row>
@@ -3333,7 +3345,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="4">
-        <f>SUM(F28:V28)</f>
+        <f t="shared" si="0"/>
         <v>5.0277777777777782E-2</v>
       </c>
       <c r="F28" s="3">
@@ -3388,31 +3400,31 @@
         <v>3.7962962962962963E-3</v>
       </c>
       <c r="W28" s="3">
-        <f>SUM(F28,H28,J28,L28,N28,P28,R28,T28)</f>
+        <f t="shared" si="1"/>
         <v>2.3900462962962964E-2</v>
       </c>
       <c r="X28" s="3">
-        <f>MIN(F28,H28,J28,L28,N28,P28,R28,T28)</f>
+        <f t="shared" si="2"/>
         <v>2.3495370370370371E-3</v>
       </c>
       <c r="Y28" s="3">
-        <f>W28/8</f>
+        <f t="shared" si="3"/>
         <v>2.9875578703703705E-3</v>
       </c>
       <c r="Z28" s="3">
-        <f>SUM(G28,I28,K28,M28,O28,Q28,S28,U28)</f>
+        <f t="shared" si="4"/>
         <v>2.2581018518518518E-2</v>
       </c>
       <c r="AA28" s="3">
-        <f>AVERAGE(G28,I28,K28,M28,O28,Q28,S28,U28)</f>
+        <f t="shared" si="5"/>
         <v>2.8226273148148147E-3</v>
       </c>
       <c r="AB28" s="1">
-        <f>W28/E28</f>
+        <f t="shared" si="6"/>
         <v>0.47536832412523017</v>
       </c>
       <c r="AC28" s="1">
-        <f>Z28/E28</f>
+        <f t="shared" si="7"/>
         <v>0.44912523020257822</v>
       </c>
     </row>
@@ -3430,7 +3442,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="4">
-        <f>SUM(F29:V29)</f>
+        <f t="shared" si="0"/>
         <v>5.0358796296296297E-2</v>
       </c>
       <c r="F29" s="3">
@@ -3485,31 +3497,31 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="W29" s="3">
-        <f>SUM(F29,H29,J29,L29,N29,P29,R29,T29)</f>
+        <f t="shared" si="1"/>
         <v>2.4861111111111112E-2</v>
       </c>
       <c r="X29" s="3">
-        <f>MIN(F29,H29,J29,L29,N29,P29,R29,T29)</f>
+        <f t="shared" si="2"/>
         <v>2.5115740740740741E-3</v>
       </c>
       <c r="Y29" s="3">
-        <f>W29/8</f>
+        <f t="shared" si="3"/>
         <v>3.107638888888889E-3</v>
       </c>
       <c r="Z29" s="3">
-        <f>SUM(G29,I29,K29,M29,O29,Q29,S29,U29)</f>
+        <f t="shared" si="4"/>
         <v>2.2025462962962958E-2</v>
       </c>
       <c r="AA29" s="3">
-        <f>AVERAGE(G29,I29,K29,M29,O29,Q29,S29,U29)</f>
+        <f t="shared" si="5"/>
         <v>2.7531828703703698E-3</v>
       </c>
       <c r="AB29" s="1">
-        <f>W29/E29</f>
+        <f t="shared" si="6"/>
         <v>0.49367961388186626</v>
       </c>
       <c r="AC29" s="1">
-        <f>Z29/E29</f>
+        <f t="shared" si="7"/>
         <v>0.43737071937485628</v>
       </c>
     </row>
@@ -3527,7 +3539,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="4">
-        <f>SUM(F30:V30)</f>
+        <f t="shared" si="0"/>
         <v>5.0486111111111107E-2</v>
       </c>
       <c r="F30" s="3">
@@ -3582,31 +3594,31 @@
         <v>3.3680555555555551E-3</v>
       </c>
       <c r="W30" s="3">
-        <f>SUM(F30,H30,J30,L30,N30,P30,R30,T30)</f>
+        <f t="shared" si="1"/>
         <v>2.5509259259259259E-2</v>
       </c>
       <c r="X30" s="3">
-        <f>MIN(F30,H30,J30,L30,N30,P30,R30,T30)</f>
+        <f t="shared" si="2"/>
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="Y30" s="3">
-        <f>W30/8</f>
+        <f t="shared" si="3"/>
         <v>3.1886574074074074E-3</v>
       </c>
       <c r="Z30" s="3">
-        <f>SUM(G30,I30,K30,M30,O30,Q30,S30,U30)</f>
+        <f t="shared" si="4"/>
         <v>2.1608796296296296E-2</v>
       </c>
       <c r="AA30" s="3">
-        <f>AVERAGE(G30,I30,K30,M30,O30,Q30,S30,U30)</f>
+        <f t="shared" si="5"/>
         <v>2.701099537037037E-3</v>
       </c>
       <c r="AB30" s="1">
-        <f>W30/E30</f>
+        <f t="shared" si="6"/>
         <v>0.50527281063732232</v>
       </c>
       <c r="AC30" s="1">
-        <f>Z30/E30</f>
+        <f t="shared" si="7"/>
         <v>0.42801467216872996</v>
       </c>
     </row>
@@ -3624,7 +3636,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="4">
-        <f>SUM(F31:V31)</f>
+        <f t="shared" si="0"/>
         <v>5.0486111111111114E-2</v>
       </c>
       <c r="F31" s="3">
@@ -3679,31 +3691,31 @@
         <v>4.2013888888888891E-3</v>
       </c>
       <c r="W31" s="3">
-        <f>SUM(F31,H31,J31,L31,N31,P31,R31,T31)</f>
+        <f t="shared" si="1"/>
         <v>2.4432870370370372E-2</v>
       </c>
       <c r="X31" s="3">
-        <f>MIN(F31,H31,J31,L31,N31,P31,R31,T31)</f>
+        <f t="shared" si="2"/>
         <v>2.4652777777777776E-3</v>
       </c>
       <c r="Y31" s="3">
-        <f>W31/8</f>
+        <f t="shared" si="3"/>
         <v>3.0541087962962965E-3</v>
       </c>
       <c r="Z31" s="3">
-        <f>SUM(G31,I31,K31,M31,O31,Q31,S31,U31)</f>
+        <f t="shared" si="4"/>
         <v>2.1851851851851851E-2</v>
       </c>
       <c r="AA31" s="3">
-        <f>AVERAGE(G31,I31,K31,M31,O31,Q31,S31,U31)</f>
+        <f t="shared" si="5"/>
         <v>2.7314814814814814E-3</v>
       </c>
       <c r="AB31" s="1">
-        <f>W31/E31</f>
+        <f t="shared" si="6"/>
         <v>0.4839523154516277</v>
       </c>
       <c r="AC31" s="1">
-        <f>Z31/E31</f>
+        <f t="shared" si="7"/>
         <v>0.43282897753324162</v>
       </c>
     </row>
@@ -3721,7 +3733,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="4">
-        <f>SUM(F32:V32)</f>
+        <f t="shared" si="0"/>
         <v>5.0636574074074077E-2</v>
       </c>
       <c r="F32" s="3">
@@ -3776,31 +3788,31 @@
         <v>4.0162037037037033E-3</v>
       </c>
       <c r="W32" s="3">
-        <f>SUM(F32,H32,J32,L32,N32,P32,R32,T32)</f>
+        <f t="shared" si="1"/>
         <v>2.4664351851851854E-2</v>
       </c>
       <c r="X32" s="3">
-        <f>MIN(F32,H32,J32,L32,N32,P32,R32,T32)</f>
+        <f t="shared" si="2"/>
         <v>2.5462962962962961E-3</v>
       </c>
       <c r="Y32" s="3">
-        <f>W32/8</f>
+        <f t="shared" si="3"/>
         <v>3.0830439814814817E-3</v>
       </c>
       <c r="Z32" s="3">
-        <f>SUM(G32,I32,K32,M32,O32,Q32,S32,U32)</f>
+        <f t="shared" si="4"/>
         <v>2.1956018518518521E-2</v>
       </c>
       <c r="AA32" s="3">
-        <f>AVERAGE(G32,I32,K32,M32,O32,Q32,S32,U32)</f>
+        <f t="shared" si="5"/>
         <v>2.7445023148148151E-3</v>
       </c>
       <c r="AB32" s="1">
-        <f>W32/E32</f>
+        <f t="shared" si="6"/>
         <v>0.48708571428571429</v>
       </c>
       <c r="AC32" s="1">
-        <f>Z32/E32</f>
+        <f t="shared" si="7"/>
         <v>0.43360000000000004</v>
       </c>
     </row>
@@ -3818,7 +3830,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="4">
-        <f>SUM(F33:V33)</f>
+        <f t="shared" si="0"/>
         <v>5.0694444444444438E-2</v>
       </c>
       <c r="F33" s="3">
@@ -3873,31 +3885,31 @@
         <v>4.1898148148148146E-3</v>
       </c>
       <c r="W33" s="3">
-        <f>SUM(F33,H33,J33,L33,N33,P33,R33,T33)</f>
+        <f t="shared" si="1"/>
         <v>2.5914351851851859E-2</v>
       </c>
       <c r="X33" s="3">
-        <f>MIN(F33,H33,J33,L33,N33,P33,R33,T33)</f>
+        <f t="shared" si="2"/>
         <v>2.615740740740741E-3</v>
       </c>
       <c r="Y33" s="3">
-        <f>W33/8</f>
+        <f t="shared" si="3"/>
         <v>3.2392939814814823E-3</v>
       </c>
       <c r="Z33" s="3">
-        <f>SUM(G33,I33,K33,M33,O33,Q33,S33,U33)</f>
+        <f t="shared" si="4"/>
         <v>2.0590277777777777E-2</v>
       </c>
       <c r="AA33" s="3">
-        <f>AVERAGE(G33,I33,K33,M33,O33,Q33,S33,U33)</f>
+        <f t="shared" si="5"/>
         <v>2.5737847222222221E-3</v>
       </c>
       <c r="AB33" s="1">
-        <f>W33/E33</f>
+        <f t="shared" si="6"/>
         <v>0.51118721461187233</v>
       </c>
       <c r="AC33" s="1">
-        <f>Z33/E33</f>
+        <f t="shared" si="7"/>
         <v>0.40616438356164386</v>
       </c>
     </row>
@@ -3915,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="4">
-        <f>SUM(F34:V34)</f>
+        <f t="shared" ref="E34:E65" si="8">SUM(F34:V34)</f>
         <v>5.0879629629629622E-2</v>
       </c>
       <c r="F34" s="3">
@@ -3970,31 +3982,31 @@
         <v>3.7152777777777774E-3</v>
       </c>
       <c r="W34" s="3">
-        <f>SUM(F34,H34,J34,L34,N34,P34,R34,T34)</f>
+        <f t="shared" ref="W34:W51" si="9">SUM(F34,H34,J34,L34,N34,P34,R34,T34)</f>
         <v>2.4918981481481486E-2</v>
       </c>
       <c r="X34" s="3">
-        <f>MIN(F34,H34,J34,L34,N34,P34,R34,T34)</f>
+        <f t="shared" ref="X34:X51" si="10">MIN(F34,H34,J34,L34,N34,P34,R34,T34)</f>
         <v>2.4652777777777776E-3</v>
       </c>
       <c r="Y34" s="3">
-        <f>W34/8</f>
+        <f t="shared" ref="Y34:Y51" si="11">W34/8</f>
         <v>3.1148726851851858E-3</v>
       </c>
       <c r="Z34" s="3">
-        <f>SUM(G34,I34,K34,M34,O34,Q34,S34,U34)</f>
+        <f t="shared" ref="Z34:Z51" si="12">SUM(G34,I34,K34,M34,O34,Q34,S34,U34)</f>
         <v>2.2245370370370367E-2</v>
       </c>
       <c r="AA34" s="3">
-        <f>AVERAGE(G34,I34,K34,M34,O34,Q34,S34,U34)</f>
+        <f t="shared" ref="AA34:AA51" si="13">AVERAGE(G34,I34,K34,M34,O34,Q34,S34,U34)</f>
         <v>2.7806712962962958E-3</v>
       </c>
       <c r="AB34" s="1">
-        <f>W34/E34</f>
+        <f t="shared" ref="AB34:AB51" si="14">W34/E34</f>
         <v>0.48976342129208389</v>
       </c>
       <c r="AC34" s="1">
-        <f>Z34/E34</f>
+        <f t="shared" ref="AC34:AC51" si="15">Z34/E34</f>
         <v>0.43721565059144679</v>
       </c>
     </row>
@@ -4012,7 +4024,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="4">
-        <f>SUM(F35:V35)</f>
+        <f t="shared" si="8"/>
         <v>5.0983796296296298E-2</v>
       </c>
       <c r="F35" s="3">
@@ -4067,31 +4079,31 @@
         <v>4.0740740740740746E-3</v>
       </c>
       <c r="W35" s="3">
-        <f>SUM(F35,H35,J35,L35,N35,P35,R35,T35)</f>
+        <f t="shared" si="9"/>
         <v>2.5335648148148149E-2</v>
       </c>
       <c r="X35" s="3">
-        <f>MIN(F35,H35,J35,L35,N35,P35,R35,T35)</f>
+        <f t="shared" si="10"/>
         <v>2.5694444444444445E-3</v>
       </c>
       <c r="Y35" s="3">
-        <f>W35/8</f>
+        <f t="shared" si="11"/>
         <v>3.1669560185185186E-3</v>
       </c>
       <c r="Z35" s="3">
-        <f>SUM(G35,I35,K35,M35,O35,Q35,S35,U35)</f>
+        <f t="shared" si="12"/>
         <v>2.1574074074074072E-2</v>
       </c>
       <c r="AA35" s="3">
-        <f>AVERAGE(G35,I35,K35,M35,O35,Q35,S35,U35)</f>
+        <f t="shared" si="13"/>
         <v>2.696759259259259E-3</v>
       </c>
       <c r="AB35" s="1">
-        <f>W35/E35</f>
+        <f t="shared" si="14"/>
         <v>0.49693530079455167</v>
       </c>
       <c r="AC35" s="1">
-        <f>Z35/E35</f>
+        <f t="shared" si="15"/>
         <v>0.42315550510783195</v>
       </c>
     </row>
@@ -4109,7 +4121,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="4">
-        <f>SUM(F36:V36)</f>
+        <f t="shared" si="8"/>
         <v>5.1238425925925923E-2</v>
       </c>
       <c r="F36" s="3">
@@ -4164,31 +4176,31 @@
         <v>3.9699074074074072E-3</v>
       </c>
       <c r="W36" s="3">
-        <f>SUM(F36,H36,J36,L36,N36,P36,R36,T36)</f>
+        <f t="shared" si="9"/>
         <v>2.5601851851851855E-2</v>
       </c>
       <c r="X36" s="3">
-        <f>MIN(F36,H36,J36,L36,N36,P36,R36,T36)</f>
+        <f t="shared" si="10"/>
         <v>2.6967592592592594E-3</v>
       </c>
       <c r="Y36" s="3">
-        <f>W36/8</f>
+        <f t="shared" si="11"/>
         <v>3.2002314814814819E-3</v>
       </c>
       <c r="Z36" s="3">
-        <f>SUM(G36,I36,K36,M36,O36,Q36,S36,U36)</f>
+        <f t="shared" si="12"/>
         <v>2.1666666666666667E-2</v>
       </c>
       <c r="AA36" s="3">
-        <f>AVERAGE(G36,I36,K36,M36,O36,Q36,S36,U36)</f>
+        <f t="shared" si="13"/>
         <v>2.7083333333333334E-3</v>
       </c>
       <c r="AB36" s="1">
-        <f>W36/E36</f>
+        <f t="shared" si="14"/>
         <v>0.49966117009261357</v>
       </c>
       <c r="AC36" s="1">
-        <f>Z36/E36</f>
+        <f t="shared" si="15"/>
         <v>0.42285972441834202</v>
       </c>
     </row>
@@ -4206,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="4">
-        <f>SUM(F37:V37)</f>
+        <f t="shared" si="8"/>
         <v>5.1296296296296305E-2</v>
       </c>
       <c r="F37" s="3">
@@ -4261,31 +4273,31 @@
         <v>3.7847222222222223E-3</v>
       </c>
       <c r="W37" s="3">
-        <f>SUM(F37,H37,J37,L37,N37,P37,R37,T37)</f>
+        <f t="shared" si="9"/>
         <v>2.5439814814814818E-2</v>
       </c>
       <c r="X37" s="3">
-        <f>MIN(F37,H37,J37,L37,N37,P37,R37,T37)</f>
+        <f t="shared" si="10"/>
         <v>2.5231481481481481E-3</v>
       </c>
       <c r="Y37" s="3">
-        <f>W37/8</f>
+        <f t="shared" si="11"/>
         <v>3.1799768518518522E-3</v>
       </c>
       <c r="Z37" s="3">
-        <f>SUM(G37,I37,K37,M37,O37,Q37,S37,U37)</f>
+        <f t="shared" si="12"/>
         <v>2.207175925925926E-2</v>
       </c>
       <c r="AA37" s="3">
-        <f>AVERAGE(G37,I37,K37,M37,O37,Q37,S37,U37)</f>
+        <f t="shared" si="13"/>
         <v>2.7589699074074075E-3</v>
       </c>
       <c r="AB37" s="1">
-        <f>W37/E37</f>
+        <f t="shared" si="14"/>
         <v>0.49593862815884476</v>
       </c>
       <c r="AC37" s="1">
-        <f>Z37/E37</f>
+        <f t="shared" si="15"/>
         <v>0.43027978339350176</v>
       </c>
     </row>
@@ -4303,7 +4315,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="4">
-        <f>SUM(F38:V38)</f>
+        <f t="shared" si="8"/>
         <v>5.1423611111111114E-2</v>
       </c>
       <c r="F38" s="3">
@@ -4358,31 +4370,31 @@
         <v>4.0972222222222226E-3</v>
       </c>
       <c r="W38" s="3">
-        <f>SUM(F38,H38,J38,L38,N38,P38,R38,T38)</f>
+        <f t="shared" si="9"/>
         <v>2.4768518518518516E-2</v>
       </c>
       <c r="X38" s="3">
-        <f>MIN(F38,H38,J38,L38,N38,P38,R38,T38)</f>
+        <f t="shared" si="10"/>
         <v>2.4305555555555556E-3</v>
       </c>
       <c r="Y38" s="3">
-        <f>W38/8</f>
+        <f t="shared" si="11"/>
         <v>3.0960648148148145E-3</v>
       </c>
       <c r="Z38" s="3">
-        <f>SUM(G38,I38,K38,M38,O38,Q38,S38,U38)</f>
+        <f t="shared" si="12"/>
         <v>2.2557870370370374E-2</v>
       </c>
       <c r="AA38" s="3">
-        <f>AVERAGE(G38,I38,K38,M38,O38,Q38,S38,U38)</f>
+        <f t="shared" si="13"/>
         <v>2.8197337962962967E-3</v>
       </c>
       <c r="AB38" s="1">
-        <f>W38/E38</f>
+        <f t="shared" si="14"/>
         <v>0.4816565383749718</v>
       </c>
       <c r="AC38" s="1">
-        <f>Z38/E38</f>
+        <f t="shared" si="15"/>
         <v>0.43866756695926179</v>
       </c>
     </row>
@@ -4400,7 +4412,7 @@
         <v>3</v>
       </c>
       <c r="E39" s="4">
-        <f>SUM(F39:V39)</f>
+        <f t="shared" si="8"/>
         <v>5.1469907407407395E-2</v>
       </c>
       <c r="F39" s="3">
@@ -4455,31 +4467,31 @@
         <v>3.9930555555555561E-3</v>
       </c>
       <c r="W39" s="3">
-        <f>SUM(F39,H39,J39,L39,N39,P39,R39,T39)</f>
+        <f t="shared" si="9"/>
         <v>2.7800925925925923E-2</v>
       </c>
       <c r="X39" s="3">
-        <f>MIN(F39,H39,J39,L39,N39,P39,R39,T39)</f>
+        <f t="shared" si="10"/>
         <v>2.5578703703703705E-3</v>
       </c>
       <c r="Y39" s="3">
-        <f>W39/8</f>
+        <f t="shared" si="11"/>
         <v>3.4751157407407404E-3</v>
       </c>
       <c r="Z39" s="3">
-        <f>SUM(G39,I39,K39,M39,O39,Q39,S39,U39)</f>
+        <f t="shared" si="12"/>
         <v>1.9675925925925923E-2</v>
       </c>
       <c r="AA39" s="3">
-        <f>AVERAGE(G39,I39,K39,M39,O39,Q39,S39,U39)</f>
+        <f t="shared" si="13"/>
         <v>2.4594907407407404E-3</v>
       </c>
       <c r="AB39" s="1">
-        <f>W39/E39</f>
+        <f t="shared" si="14"/>
         <v>0.54013941983359581</v>
       </c>
       <c r="AC39" s="1">
-        <f>Z39/E39</f>
+        <f t="shared" si="15"/>
         <v>0.38228018889138748</v>
       </c>
     </row>
@@ -4497,7 +4509,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="4">
-        <f>SUM(F40:V40)</f>
+        <f t="shared" si="8"/>
         <v>5.1481481481481489E-2</v>
       </c>
       <c r="F40" s="3">
@@ -4552,31 +4564,31 @@
         <v>5.6365740740740742E-3</v>
       </c>
       <c r="W40" s="3">
-        <f>SUM(F40,H40,J40,L40,N40,P40,R40,T40)</f>
+        <f t="shared" si="9"/>
         <v>2.4988425925925924E-2</v>
       </c>
       <c r="X40" s="3">
-        <f>MIN(F40,H40,J40,L40,N40,P40,R40,T40)</f>
+        <f t="shared" si="10"/>
         <v>2.5578703703703705E-3</v>
       </c>
       <c r="Y40" s="3">
-        <f>W40/8</f>
+        <f t="shared" si="11"/>
         <v>3.1235532407407405E-3</v>
       </c>
       <c r="Z40" s="3">
-        <f>SUM(G40,I40,K40,M40,O40,Q40,S40,U40)</f>
+        <f t="shared" si="12"/>
         <v>2.0856481481481483E-2</v>
       </c>
       <c r="AA40" s="3">
-        <f>AVERAGE(G40,I40,K40,M40,O40,Q40,S40,U40)</f>
+        <f t="shared" si="13"/>
         <v>2.6070601851851853E-3</v>
       </c>
       <c r="AB40" s="1">
-        <f>W40/E40</f>
+        <f t="shared" si="14"/>
         <v>0.48538669064748191</v>
       </c>
       <c r="AC40" s="1">
-        <f>Z40/E40</f>
+        <f t="shared" si="15"/>
         <v>0.40512589928057552</v>
       </c>
     </row>
@@ -4594,7 +4606,7 @@
         <v>5</v>
       </c>
       <c r="E41" s="4">
-        <f>SUM(F41:V41)</f>
+        <f t="shared" si="8"/>
         <v>5.1504629629629629E-2</v>
       </c>
       <c r="F41" s="3">
@@ -4649,31 +4661,31 @@
         <v>3.6226851851851854E-3</v>
       </c>
       <c r="W41" s="3">
-        <f>SUM(F41,H41,J41,L41,N41,P41,R41,T41)</f>
+        <f t="shared" si="9"/>
         <v>2.3842592592592592E-2</v>
       </c>
       <c r="X41" s="3">
-        <f>MIN(F41,H41,J41,L41,N41,P41,R41,T41)</f>
+        <f t="shared" si="10"/>
         <v>2.4074074074074076E-3</v>
       </c>
       <c r="Y41" s="3">
-        <f>W41/8</f>
+        <f t="shared" si="11"/>
         <v>2.980324074074074E-3</v>
       </c>
       <c r="Z41" s="3">
-        <f>SUM(G41,I41,K41,M41,O41,Q41,S41,U41)</f>
+        <f t="shared" si="12"/>
         <v>2.403935185185185E-2</v>
       </c>
       <c r="AA41" s="3">
-        <f>AVERAGE(G41,I41,K41,M41,O41,Q41,S41,U41)</f>
+        <f t="shared" si="13"/>
         <v>3.0049189814814812E-3</v>
       </c>
       <c r="AB41" s="1">
-        <f>W41/E41</f>
+        <f t="shared" si="14"/>
         <v>0.46292134831460674</v>
       </c>
       <c r="AC41" s="1">
-        <f>Z41/E41</f>
+        <f t="shared" si="15"/>
         <v>0.46674157303370784</v>
       </c>
     </row>
@@ -4691,7 +4703,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="4">
-        <f>SUM(F42:V42)</f>
+        <f t="shared" si="8"/>
         <v>5.1585648148148151E-2</v>
       </c>
       <c r="F42" s="3">
@@ -4746,31 +4758,31 @@
         <v>3.8888888888888883E-3</v>
       </c>
       <c r="W42" s="3">
-        <f>SUM(F42,H42,J42,L42,N42,P42,R42,T42)</f>
+        <f t="shared" si="9"/>
         <v>2.5613425925925928E-2</v>
       </c>
       <c r="X42" s="3">
-        <f>MIN(F42,H42,J42,L42,N42,P42,R42,T42)</f>
+        <f t="shared" si="10"/>
         <v>2.6967592592592594E-3</v>
       </c>
       <c r="Y42" s="3">
-        <f>W42/8</f>
+        <f t="shared" si="11"/>
         <v>3.201678240740741E-3</v>
       </c>
       <c r="Z42" s="3">
-        <f>SUM(G42,I42,K42,M42,O42,Q42,S42,U42)</f>
+        <f t="shared" si="12"/>
         <v>2.2083333333333333E-2</v>
       </c>
       <c r="AA42" s="3">
-        <f>AVERAGE(G42,I42,K42,M42,O42,Q42,S42,U42)</f>
+        <f t="shared" si="13"/>
         <v>2.7604166666666667E-3</v>
       </c>
       <c r="AB42" s="1">
-        <f>W42/E42</f>
+        <f t="shared" si="14"/>
         <v>0.49652232443347544</v>
       </c>
       <c r="AC42" s="1">
-        <f>Z42/E42</f>
+        <f t="shared" si="15"/>
         <v>0.42809064393089519</v>
       </c>
     </row>
@@ -4788,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="4">
-        <f>SUM(F43:V43)</f>
+        <f t="shared" si="8"/>
         <v>5.1608796296296292E-2</v>
       </c>
       <c r="F43" s="3">
@@ -4843,31 +4855,31 @@
         <v>3.6689814814814814E-3</v>
       </c>
       <c r="W43" s="3">
-        <f>SUM(F43,H43,J43,L43,N43,P43,R43,T43)</f>
+        <f t="shared" si="9"/>
         <v>2.4513888888888887E-2</v>
       </c>
       <c r="X43" s="3">
-        <f>MIN(F43,H43,J43,L43,N43,P43,R43,T43)</f>
+        <f t="shared" si="10"/>
         <v>2.615740740740741E-3</v>
       </c>
       <c r="Y43" s="3">
-        <f>W43/8</f>
+        <f t="shared" si="11"/>
         <v>3.0642361111111109E-3</v>
       </c>
       <c r="Z43" s="3">
-        <f>SUM(G43,I43,K43,M43,O43,Q43,S43,U43)</f>
+        <f t="shared" si="12"/>
         <v>2.3425925925925926E-2</v>
       </c>
       <c r="AA43" s="3">
-        <f>AVERAGE(G43,I43,K43,M43,O43,Q43,S43,U43)</f>
+        <f t="shared" si="13"/>
         <v>2.9282407407407408E-3</v>
       </c>
       <c r="AB43" s="1">
-        <f>W43/E43</f>
+        <f t="shared" si="14"/>
         <v>0.47499439336174032</v>
       </c>
       <c r="AC43" s="1">
-        <f>Z43/E43</f>
+        <f t="shared" si="15"/>
         <v>0.4539134335052703</v>
       </c>
     </row>
@@ -4885,7 +4897,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="4">
-        <f>SUM(F44:V44)</f>
+        <f t="shared" si="8"/>
         <v>5.1631944444444439E-2</v>
       </c>
       <c r="F44" s="3">
@@ -4940,31 +4952,31 @@
         <v>3.5763888888888894E-3</v>
       </c>
       <c r="W44" s="3">
-        <f>SUM(F44,H44,J44,L44,N44,P44,R44,T44)</f>
+        <f t="shared" si="9"/>
         <v>2.4259259259259258E-2</v>
       </c>
       <c r="X44" s="3">
-        <f>MIN(F44,H44,J44,L44,N44,P44,R44,T44)</f>
+        <f t="shared" si="10"/>
         <v>2.3842592592592591E-3</v>
       </c>
       <c r="Y44" s="3">
-        <f>W44/8</f>
+        <f t="shared" si="11"/>
         <v>3.0324074074074073E-3</v>
       </c>
       <c r="Z44" s="3">
-        <f>SUM(G44,I44,K44,M44,O44,Q44,S44,U44)</f>
+        <f t="shared" si="12"/>
         <v>2.3796296296296295E-2</v>
       </c>
       <c r="AA44" s="3">
-        <f>AVERAGE(G44,I44,K44,M44,O44,Q44,S44,U44)</f>
+        <f t="shared" si="13"/>
         <v>2.9745370370370368E-3</v>
       </c>
       <c r="AB44" s="1">
-        <f>W44/E44</f>
+        <f t="shared" si="14"/>
         <v>0.4698498094597624</v>
       </c>
       <c r="AC44" s="1">
-        <f>Z44/E44</f>
+        <f t="shared" si="15"/>
         <v>0.46088321004259136</v>
       </c>
     </row>
@@ -4982,7 +4994,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="4">
-        <f>SUM(F45:V45)</f>
+        <f t="shared" si="8"/>
         <v>5.1759259259259255E-2</v>
       </c>
       <c r="F45" s="3">
@@ -5037,31 +5049,31 @@
         <v>3.6111111111111114E-3</v>
       </c>
       <c r="W45" s="3">
-        <f>SUM(F45,H45,J45,L45,N45,P45,R45,T45)</f>
+        <f t="shared" si="9"/>
         <v>2.4363425925925927E-2</v>
       </c>
       <c r="X45" s="3">
-        <f>MIN(F45,H45,J45,L45,N45,P45,R45,T45)</f>
+        <f t="shared" si="10"/>
         <v>2.5462962962962961E-3</v>
       </c>
       <c r="Y45" s="3">
-        <f>W45/8</f>
+        <f t="shared" si="11"/>
         <v>3.0454282407407409E-3</v>
       </c>
       <c r="Z45" s="3">
-        <f>SUM(G45,I45,K45,M45,O45,Q45,S45,U45)</f>
+        <f t="shared" si="12"/>
         <v>2.3784722222222218E-2</v>
       </c>
       <c r="AA45" s="3">
-        <f>AVERAGE(G45,I45,K45,M45,O45,Q45,S45,U45)</f>
+        <f t="shared" si="13"/>
         <v>2.9730902777777772E-3</v>
       </c>
       <c r="AB45" s="1">
-        <f>W45/E45</f>
+        <f t="shared" si="14"/>
         <v>0.47070661896243299</v>
       </c>
       <c r="AC45" s="1">
-        <f>Z45/E45</f>
+        <f t="shared" si="15"/>
         <v>0.45952593917710194</v>
       </c>
     </row>
@@ -5079,7 +5091,7 @@
         <v>2</v>
       </c>
       <c r="E46" s="4">
-        <f>SUM(F46:V46)</f>
+        <f t="shared" si="8"/>
         <v>5.1909722222222225E-2</v>
       </c>
       <c r="F46" s="3">
@@ -5134,31 +5146,31 @@
         <v>4.4560185185185189E-3</v>
       </c>
       <c r="W46" s="3">
-        <f>SUM(F46,H46,J46,L46,N46,P46,R46,T46)</f>
+        <f t="shared" si="9"/>
         <v>2.7592592592592589E-2</v>
       </c>
       <c r="X46" s="3">
-        <f>MIN(F46,H46,J46,L46,N46,P46,R46,T46)</f>
+        <f t="shared" si="10"/>
         <v>2.7314814814814819E-3</v>
       </c>
       <c r="Y46" s="3">
-        <f>W46/8</f>
+        <f t="shared" si="11"/>
         <v>3.4490740740740736E-3</v>
       </c>
       <c r="Z46" s="3">
-        <f>SUM(G46,I46,K46,M46,O46,Q46,S46,U46)</f>
+        <f t="shared" si="12"/>
         <v>1.9861111111111111E-2</v>
       </c>
       <c r="AA46" s="3">
-        <f>AVERAGE(G46,I46,K46,M46,O46,Q46,S46,U46)</f>
+        <f t="shared" si="13"/>
         <v>2.4826388888888888E-3</v>
       </c>
       <c r="AB46" s="1">
-        <f>W46/E46</f>
+        <f t="shared" si="14"/>
         <v>0.53154960981047927</v>
       </c>
       <c r="AC46" s="1">
-        <f>Z46/E46</f>
+        <f t="shared" si="15"/>
         <v>0.38260869565217387</v>
       </c>
     </row>
@@ -5176,7 +5188,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="4">
-        <f>SUM(F47:V47)</f>
+        <f t="shared" si="8"/>
         <v>5.2013888888888901E-2</v>
       </c>
       <c r="F47" s="3">
@@ -5231,31 +5243,31 @@
         <v>3.6342592592592594E-3</v>
       </c>
       <c r="W47" s="3">
-        <f>SUM(F47,H47,J47,L47,N47,P47,R47,T47)</f>
+        <f t="shared" si="9"/>
         <v>2.4236111111111108E-2</v>
       </c>
       <c r="X47" s="3">
-        <f>MIN(F47,H47,J47,L47,N47,P47,R47,T47)</f>
+        <f t="shared" si="10"/>
         <v>2.488425925925926E-3</v>
       </c>
       <c r="Y47" s="3">
-        <f>W47/8</f>
+        <f t="shared" si="11"/>
         <v>3.0295138888888884E-3</v>
       </c>
       <c r="Z47" s="3">
-        <f>SUM(G47,I47,K47,M47,O47,Q47,S47,U47)</f>
+        <f t="shared" si="12"/>
         <v>2.4143518518518519E-2</v>
       </c>
       <c r="AA47" s="3">
-        <f>AVERAGE(G47,I47,K47,M47,O47,Q47,S47,U47)</f>
+        <f t="shared" si="13"/>
         <v>3.0179398148148149E-3</v>
       </c>
       <c r="AB47" s="1">
-        <f>W47/E47</f>
+        <f t="shared" si="14"/>
         <v>0.46595460614152184</v>
       </c>
       <c r="AC47" s="1">
-        <f>Z47/E47</f>
+        <f t="shared" si="15"/>
         <v>0.46417445482866032</v>
       </c>
     </row>
@@ -5273,7 +5285,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="4">
-        <f>SUM(F48:V48)</f>
+        <f t="shared" si="8"/>
         <v>5.2013888888888901E-2</v>
       </c>
       <c r="F48" s="3">
@@ -5328,31 +5340,31 @@
         <v>3.6689814814814814E-3</v>
       </c>
       <c r="W48" s="3">
-        <f>SUM(F48,H48,J48,L48,N48,P48,R48,T48)</f>
+        <f t="shared" si="9"/>
         <v>2.6099537037037036E-2</v>
       </c>
       <c r="X48" s="3">
-        <f>MIN(F48,H48,J48,L48,N48,P48,R48,T48)</f>
+        <f t="shared" si="10"/>
         <v>2.685185185185185E-3</v>
       </c>
       <c r="Y48" s="3">
-        <f>W48/8</f>
+        <f t="shared" si="11"/>
         <v>3.2624421296296295E-3</v>
       </c>
       <c r="Z48" s="3">
-        <f>SUM(G48,I48,K48,M48,O48,Q48,S48,U48)</f>
+        <f t="shared" si="12"/>
         <v>2.2245370370370367E-2</v>
       </c>
       <c r="AA48" s="3">
-        <f>AVERAGE(G48,I48,K48,M48,O48,Q48,S48,U48)</f>
+        <f t="shared" si="13"/>
         <v>2.7806712962962958E-3</v>
       </c>
       <c r="AB48" s="1">
-        <f>W48/E48</f>
+        <f t="shared" si="14"/>
         <v>0.50178015131286147</v>
       </c>
       <c r="AC48" s="1">
-        <f>Z48/E48</f>
+        <f t="shared" si="15"/>
         <v>0.42768135291499759</v>
       </c>
     </row>
@@ -5370,7 +5382,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="4">
-        <f>SUM(F49:V49)</f>
+        <f t="shared" si="8"/>
         <v>5.2025462962962961E-2</v>
       </c>
       <c r="F49" s="3">
@@ -5425,31 +5437,31 @@
         <v>3.6921296296296298E-3</v>
       </c>
       <c r="W49" s="3">
-        <f>SUM(F49,H49,J49,L49,N49,P49,R49,T49)</f>
+        <f t="shared" si="9"/>
         <v>2.5196759259259259E-2</v>
       </c>
       <c r="X49" s="3">
-        <f>MIN(F49,H49,J49,L49,N49,P49,R49,T49)</f>
+        <f t="shared" si="10"/>
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="Y49" s="3">
-        <f>W49/8</f>
+        <f t="shared" si="11"/>
         <v>3.1495949074074074E-3</v>
       </c>
       <c r="Z49" s="3">
-        <f>SUM(G49,I49,K49,M49,O49,Q49,S49,U49)</f>
+        <f t="shared" si="12"/>
         <v>2.3136574074074073E-2</v>
       </c>
       <c r="AA49" s="3">
-        <f>AVERAGE(G49,I49,K49,M49,O49,Q49,S49,U49)</f>
+        <f t="shared" si="13"/>
         <v>2.8920717592592592E-3</v>
       </c>
       <c r="AB49" s="1">
-        <f>W49/E49</f>
+        <f t="shared" si="14"/>
         <v>0.48431590656284762</v>
       </c>
       <c r="AC49" s="1">
-        <f>Z49/E49</f>
+        <f t="shared" si="15"/>
         <v>0.44471635150166855</v>
       </c>
     </row>
@@ -5467,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="4">
-        <f>SUM(F50:V50)</f>
+        <f t="shared" si="8"/>
         <v>5.2118055555555556E-2</v>
       </c>
       <c r="F50" s="3">
@@ -5522,31 +5534,31 @@
         <v>3.8541666666666668E-3</v>
       </c>
       <c r="W50" s="3">
-        <f>SUM(F50,H50,J50,L50,N50,P50,R50,T50)</f>
+        <f t="shared" si="9"/>
         <v>2.510416666666667E-2</v>
       </c>
       <c r="X50" s="3">
-        <f>MIN(F50,H50,J50,L50,N50,P50,R50,T50)</f>
+        <f t="shared" si="10"/>
         <v>2.6041666666666665E-3</v>
       </c>
       <c r="Y50" s="3">
-        <f>W50/8</f>
+        <f t="shared" si="11"/>
         <v>3.1380208333333338E-3</v>
       </c>
       <c r="Z50" s="3">
-        <f>SUM(G50,I50,K50,M50,O50,Q50,S50,U50)</f>
+        <f t="shared" si="12"/>
         <v>2.3159722222222224E-2</v>
       </c>
       <c r="AA50" s="3">
-        <f>AVERAGE(G50,I50,K50,M50,O50,Q50,S50,U50)</f>
+        <f t="shared" si="13"/>
         <v>2.894965277777778E-3</v>
       </c>
       <c r="AB50" s="1">
-        <f>W50/E50</f>
+        <f t="shared" si="14"/>
         <v>0.48167888074616927</v>
       </c>
       <c r="AC50" s="1">
-        <f>Z50/E50</f>
+        <f t="shared" si="15"/>
         <v>0.44437041972018659</v>
       </c>
     </row>
@@ -5564,7 +5576,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="4">
-        <f>SUM(F51:V51)</f>
+        <f t="shared" si="8"/>
         <v>5.2337962962962968E-2</v>
       </c>
       <c r="F51" s="3">
@@ -5619,37 +5631,37 @@
         <v>3.6689814814814814E-3</v>
       </c>
       <c r="W51" s="3">
-        <f>SUM(F51,H51,J51,L51,N51,P51,R51,T51)</f>
+        <f t="shared" si="9"/>
         <v>2.6122685185185186E-2</v>
       </c>
       <c r="X51" s="3">
-        <f>MIN(F51,H51,J51,L51,N51,P51,R51,T51)</f>
+        <f t="shared" si="10"/>
         <v>2.7893518518518519E-3</v>
       </c>
       <c r="Y51" s="3">
-        <f>W51/8</f>
+        <f t="shared" si="11"/>
         <v>3.2653356481481483E-3</v>
       </c>
       <c r="Z51" s="3">
-        <f>SUM(G51,I51,K51,M51,O51,Q51,S51,U51)</f>
+        <f t="shared" si="12"/>
         <v>2.25462962962963E-2</v>
       </c>
       <c r="AA51" s="3">
-        <f>AVERAGE(G51,I51,K51,M51,O51,Q51,S51,U51)</f>
+        <f t="shared" si="13"/>
         <v>2.8182870370370375E-3</v>
       </c>
       <c r="AB51" s="1">
-        <f>W51/E51</f>
+        <f t="shared" si="14"/>
         <v>0.49911543564794336</v>
       </c>
       <c r="AC51" s="1">
-        <f>Z51/E51</f>
+        <f t="shared" si="15"/>
         <v>0.43078283945157014</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC51" xr:uid="{096AFD92-BFB8-4CAE-A981-A5D720DBDAA9}">
-    <sortState ref="A2:AC51">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC51">
       <sortCondition ref="E2:E51"/>
       <sortCondition ref="D2:D51"/>
     </sortState>
